--- a/CF_ESP/CATALOGOS/Anexo 4.xlsx
+++ b/CF_ESP/CATALOGOS/Anexo 4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a4c8ce57d2d00b7c/Documentos/Stagged/ION/Analisis/CF_ESP/CATALOGOS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/65a63616e5f6ec42/Desktop/DOCUMENTOS_IMPERA/ION/CF_ESP/CATALOGOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38492423-973E-40C3-B277-8DCFDBFB230C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{514445CD-D413-4276-A1AA-E3A10EEC9300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81787695-076D-464F-B124-29A4C28CE970}"/>
   <bookViews>
-    <workbookView xWindow="3800" yWindow="3800" windowWidth="29920" windowHeight="16020" xr2:uid="{32BCE2EC-323C-4A4F-9FB0-458F08A4943A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{80DA9B8E-27DC-49AA-8676-D0CD41EB488E}"/>
   </bookViews>
   <sheets>
     <sheet name="Anexo 4" sheetId="1" r:id="rId1"/>
@@ -39,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
-  <si>
-    <t>Anexo 4</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>CLAVE</t>
   </si>
@@ -138,7 +135,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,30 +144,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="14"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -247,18 +232,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -599,129 +581,123 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6687ECEA-18A6-459D-B880-357ED8D8A8A1}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82588772-F79F-4C0A-A98E-7D6F304F08E2}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="46.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="7" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="7" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="7" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="7" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="7" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="C7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="7" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="C8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="7" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
+      <c r="B9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="C9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="7" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
+      <c r="B10" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C10" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
